--- a/03_Outputs/all/01_TablasDescriptivas/idx7_gini_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx7_gini_vr.xlsx
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2826123026677476</v>
+        <v>0.2826123026677477</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>14.13061513338738</v>
+        <v>14.13061513338739</v>
       </c>
       <c r="C7">
         <v>2</v>
